--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486346_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486346_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>K. SMITH</t>
+          <t>G. KALSCHEUR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.918</v>
+        <v>5.9296</v>
       </c>
       <c r="E2" t="n">
-        <v>4.336</v>
+        <v>4.8305</v>
       </c>
       <c r="F2" t="n">
-        <v>1.582</v>
+        <v>1.0991</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2765</v>
+        <v>5.3043</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0804</v>
+        <v>0.3439</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1961</v>
+        <v>4.9605</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9857</v>
+        <v>6.13</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6853</v>
+        <v>0.4292</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3005</v>
+        <v>5.7008</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2907</v>
+        <v>-0.8257</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3951</v>
+        <v>-0.0854</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1044</v>
+        <v>-0.7403</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7401</v>
+        <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7285</v>
+        <v>-0.3524</v>
       </c>
       <c r="T2" t="n">
-        <v>3.1773</v>
+        <v>0.1154</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4488</v>
+        <v>-0.4678</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.7395</v>
+        <v>0.7602</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7395</v>
+        <v>0.7602</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. KALSCHEUR</t>
+          <t>K. SMITH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9478</v>
+        <v>4.5075</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7562</v>
+        <v>2.7714</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1916</v>
+        <v>1.7361</v>
       </c>
       <c r="G3" t="n">
-        <v>5.3043</v>
+        <v>3.2765</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3439</v>
+        <v>2.0804</v>
       </c>
       <c r="I3" t="n">
-        <v>4.9605</v>
+        <v>1.1961</v>
       </c>
       <c r="J3" t="n">
-        <v>6.13</v>
+        <v>2.9857</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4292</v>
+        <v>1.6853</v>
       </c>
       <c r="L3" t="n">
-        <v>5.7008</v>
+        <v>1.3005</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8257</v>
+        <v>0.2907</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0854</v>
+        <v>0.3951</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7403</v>
+        <v>-0.1044</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3926</v>
+        <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3342</v>
+        <v>1.318</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9589</v>
+        <v>1.6127</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3753</v>
+        <v>-0.2947</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7602</v>
+        <v>-0.7395</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7602</v>
+        <v>-0.7395</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. OKANU</t>
+          <t>S. MC DONNELL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1564</v>
+        <v>4.1748</v>
       </c>
       <c r="E4" t="n">
-        <v>0.664</v>
+        <v>2.8857</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4923</v>
+        <v>1.289</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3998</v>
+        <v>1.1999</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9153</v>
+        <v>2.1258</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5155999999999999</v>
+        <v>-0.926</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.8595</v>
+        <v>2.3905</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.0125</v>
+        <v>2.4272</v>
       </c>
       <c r="L4" t="n">
-        <v>0.153</v>
+        <v>-0.0366</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4597</v>
+        <v>-1.1907</v>
       </c>
       <c r="N4" t="n">
-        <v>0.09710000000000001</v>
+        <v>-0.3013</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3626</v>
+        <v>-0.8893</v>
       </c>
       <c r="P4" t="n">
         <v>0.435</v>
@@ -766,28 +766,28 @@
         <v>2.6101</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7519</v>
+        <v>0.0847</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8736</v>
+        <v>0.2151</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1217</v>
+        <v>-0.1304</v>
       </c>
       <c r="V4" t="n">
-        <v>3.3692</v>
+        <v>2.4552</v>
       </c>
       <c r="W4" t="n">
-        <v>2.8249</v>
+        <v>2.4552</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5443</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. MC DONNELL</t>
+          <t>R. DIAS MARQUES LISBOA SANTOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0677</v>
+        <v>3.6899</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5937</v>
+        <v>3.5266</v>
       </c>
       <c r="F5" t="n">
-        <v>1.474</v>
+        <v>0.1633</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1999</v>
+        <v>3.3838</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1258</v>
+        <v>1.1072</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.926</v>
+        <v>2.2766</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3905</v>
+        <v>4.4915</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4272</v>
+        <v>0.6451</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0366</v>
+        <v>3.8465</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1907</v>
+        <v>-1.1077</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3013</v>
+        <v>0.4621</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8893</v>
+        <v>-1.5698</v>
       </c>
       <c r="P5" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>2.6101</v>
+        <v>2.3926</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0224</v>
+        <v>0.131</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0769</v>
+        <v>0.1226</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0545</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>2.4552</v>
+        <v>-1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>2.4552</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ PEREZ</t>
+          <t>C. OKANU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.7902</v>
+        <v>3.6854</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3049</v>
+        <v>0.2855</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4853</v>
+        <v>3.3999</v>
       </c>
       <c r="G6" t="n">
-        <v>5.0228</v>
+        <v>-0.3998</v>
       </c>
       <c r="H6" t="n">
-        <v>2.9956</v>
+        <v>-0.9153</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0272</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>3.803</v>
+        <v>-0.8595</v>
       </c>
       <c r="K6" t="n">
-        <v>2.8834</v>
+        <v>-1.0125</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9196</v>
+        <v>0.153</v>
       </c>
       <c r="M6" t="n">
-        <v>1.2198</v>
+        <v>0.4597</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1122</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>1.1076</v>
+        <v>0.3626</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q6" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9576</v>
+        <v>2.6101</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0804</v>
+        <v>0.2809</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4817</v>
+        <v>0.4951</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.5621</v>
+        <v>-0.2142</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9347</v>
+        <v>3.3692</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1952</v>
+        <v>2.8249</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.13</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. DIAS MARQUES LISBOA SANTOS</t>
+          <t>I. VAZQUEZ PEREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7727</v>
+        <v>3.6822</v>
       </c>
       <c r="E7" t="n">
-        <v>2.856</v>
+        <v>2.8578</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0833</v>
+        <v>0.8244</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3838</v>
+        <v>5.0228</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1072</v>
+        <v>2.9956</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2766</v>
+        <v>2.0272</v>
       </c>
       <c r="J7" t="n">
-        <v>4.4915</v>
+        <v>3.803</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6451</v>
+        <v>2.8834</v>
       </c>
       <c r="L7" t="n">
-        <v>3.8465</v>
+        <v>0.9196</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1077</v>
+        <v>1.2198</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4621</v>
+        <v>0.1122</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5698</v>
+        <v>1.1076</v>
       </c>
       <c r="P7" t="n">
-        <v>1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3926</v>
+        <v>1.9576</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7862</v>
+        <v>-0.1884</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.548</v>
+        <v>1.0347</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2382</v>
+        <v>-1.223</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.13</v>
+        <v>-0.9347</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X7" t="n">
         <v>-1.13</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. GILL</t>
+          <t>C. JÜRGENS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4921</v>
+        <v>1.2904</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0999</v>
+        <v>-0.1316</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3921</v>
+        <v>1.4221</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3272</v>
+        <v>-1.1502</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5018</v>
+        <v>-1.4658</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1745</v>
+        <v>0.3156</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1098</v>
+        <v>-2.4705</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1579</v>
+        <v>-1.9765</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2677</v>
+        <v>-0.494</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2174</v>
+        <v>1.3203</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6597</v>
+        <v>0.5107</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4423</v>
+        <v>0.8096</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7401</v>
+        <v>3.0451</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7401</v>
+        <v>3.0451</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3595</v>
+        <v>1.0905</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5997</v>
+        <v>1.2089</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2401</v>
+        <v>-0.1184</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9347</v>
+        <v>-1.695</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3904</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.3252</v>
+        <v>-2.8249</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. JÜRGENS</t>
+          <t>R. GILL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0168</v>
+        <v>1.1337</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4669</v>
+        <v>0.9882</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4837</v>
+        <v>0.1456</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1502</v>
+        <v>0.3272</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4658</v>
+        <v>0.5018</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3156</v>
+        <v>-0.1745</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.4705</v>
+        <v>0.1098</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.9765</v>
+        <v>-0.1579</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.494</v>
+        <v>0.2677</v>
       </c>
       <c r="M9" t="n">
-        <v>1.3203</v>
+        <v>0.2174</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5107</v>
+        <v>0.6597</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8096</v>
+        <v>-0.4423</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0451</v>
+        <v>1.7401</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.0451</v>
+        <v>1.7401</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8169</v>
+        <v>0.0012</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8736</v>
+        <v>0.4879</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0567</v>
+        <v>-0.4867</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.695</v>
+        <v>-0.9347</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>0.3904</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.8249</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6147</v>
+        <v>0.3286</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2258</v>
+        <v>-0.375</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6111</v>
+        <v>0.7035</v>
       </c>
       <c r="G10" t="n">
         <v>1.5429</v>
@@ -1234,13 +1234,13 @@
         <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8324</v>
+        <v>0.1109</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3425</v>
+        <v>0.5083</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4899</v>
+        <v>-0.3975</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3252</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6228</v>
+        <v>-0.6391</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.21</v>
+        <v>-0.918</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.2789</v>
       </c>
       <c r="G11" t="n">
         <v>-0.782</v>
@@ -1312,13 +1312,13 @@
         <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2536</v>
+        <v>-0.2698</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0769</v>
+        <v>0.2151</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1767</v>
+        <v>-0.4849</v>
       </c>
       <c r="V11" t="n">
         <v>0.1952</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2008</v>
+        <v>-3.7172</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4862</v>
+        <v>-2.1568</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7145</v>
+        <v>-1.5604</v>
       </c>
       <c r="G12" t="n">
         <v>-4.1107</v>
@@ -1390,13 +1390,13 @@
         <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1699</v>
+        <v>0.6534</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6187</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4488</v>
+        <v>-0.2947</v>
       </c>
       <c r="V12" t="n">
         <v>-1.13</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>23.7234</v>
+        <v>24.0658</v>
       </c>
       <c r="E13" t="n">
-        <v>14.2218</v>
+        <v>14.5643</v>
       </c>
       <c r="F13" t="n">
-        <v>9.501500000000002</v>
+        <v>9.5015</v>
       </c>
       <c r="G13" t="n">
         <v>13.6147</v>
@@ -1444,7 +1444,7 @@
         <v>12.309</v>
       </c>
       <c r="K13" t="n">
-        <v>4.260700000000001</v>
+        <v>4.2607</v>
       </c>
       <c r="L13" t="n">
         <v>8.048599999999999</v>
@@ -1468,16 +1468,16 @@
         <v>21.7508</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5175</v>
+        <v>2.86</v>
       </c>
       <c r="T13" t="n">
-        <v>6.6214</v>
+        <v>6.9639</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.103800000000001</v>
+        <v>-4.1039</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.109299999999999</v>
+        <v>-1.1093</v>
       </c>
       <c r="W13" t="n">
         <v>8.3416</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.2898</v>
+        <v>6.6366</v>
       </c>
       <c r="E14" t="n">
-        <v>5.5828</v>
+        <v>5.8063</v>
       </c>
       <c r="F14" t="n">
-        <v>0.707</v>
+        <v>0.8303</v>
       </c>
       <c r="G14" t="n">
         <v>-0.0014</v>
@@ -1546,13 +1546,13 @@
         <v>2.3926</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0053</v>
+        <v>-0.6585</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1334</v>
+        <v>0.0901</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.872</v>
+        <v>-0.7487</v>
       </c>
       <c r="V14" t="n">
         <v>8.166600000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.398</v>
+        <v>2.2728</v>
       </c>
       <c r="E15" t="n">
-        <v>5.3585</v>
+        <v>4.9115</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9605</v>
+        <v>-2.6386</v>
       </c>
       <c r="G15" t="n">
         <v>3.0966</v>
@@ -1624,13 +1624,13 @@
         <v>1.7401</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8494</v>
+        <v>-0.2758</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4747</v>
+        <v>0.0277</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3747</v>
+        <v>-0.3034</v>
       </c>
       <c r="V15" t="n">
         <v>-0.113</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. DEBAUT</t>
+          <t>M. STILMA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7586000000000001</v>
+        <v>-1.395</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0847</v>
+        <v>-1.2203</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.674</v>
+        <v>-0.1747</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8077</v>
+        <v>0.1544</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9367</v>
+        <v>0.1823</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1291</v>
+        <v>-0.0279</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.3989</v>
+        <v>0.2622</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.3989</v>
+        <v>0.9307</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0.6686</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5911999999999999</v>
+        <v>-0.1077</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4621</v>
+        <v>-0.7484</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1291</v>
+        <v>0.6407</v>
       </c>
       <c r="P16" t="n">
-        <v>0.87</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R16" t="n">
         <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3737</v>
+        <v>-0.0916</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0537</v>
+        <v>0.6501</v>
       </c>
       <c r="U16" t="n">
-        <v>0.32</v>
+        <v>-0.7418</v>
       </c>
       <c r="V16" t="n">
-        <v>-3.1947</v>
+        <v>0.9347</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.7395</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.4552</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. STILMA</t>
+          <t>L. DEBAUT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7727</v>
+        <v>-2.0649</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4439</v>
+        <v>-0.867</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3288</v>
+        <v>-1.1979</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1544</v>
+        <v>-0.8077</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1823</v>
+        <v>-0.9367</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0279</v>
+        <v>0.1291</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2622</v>
+        <v>-1.3989</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9307</v>
+        <v>-1.3989</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6686</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1077</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7484</v>
+        <v>0.4621</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6407</v>
+        <v>0.1291</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.3926</v>
+        <v>0.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4693</v>
+        <v>1.0674</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4266</v>
+        <v>1.2714</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8959</v>
+        <v>-0.204</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9347</v>
+        <v>-3.1947</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>-0.7395</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1952</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. STUMBRIS</t>
+          <t>C. DIAZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.3408</v>
+        <v>-4.5896</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6455</v>
+        <v>-1.9705</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.6953</v>
+        <v>-2.6191</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.485</v>
+        <v>-2.2582</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.814</v>
+        <v>-1.612</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.671</v>
+        <v>-0.6463</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.4319</v>
+        <v>0.8234</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.7977</v>
+        <v>-0.2492</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3658</v>
+        <v>1.0726</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.053</v>
+        <v>-3.0817</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0162</v>
+        <v>-1.3628</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.0368</v>
+        <v>-1.7188</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6525</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7401</v>
+        <v>2.1751</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2965</v>
+        <v>-0.1754</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6788</v>
+        <v>0.4687</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.3823</v>
+        <v>-0.6441</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1952</v>
+        <v>-1.0684</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.0684</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.2091</v>
+        <v>-5.2168</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.7732</v>
+        <v>-4.9967</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4359</v>
+        <v>-0.2201</v>
       </c>
       <c r="G19" t="n">
         <v>-3.0444</v>
@@ -1936,13 +1936,13 @@
         <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0941</v>
+        <v>-0.1018</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8411999999999999</v>
+        <v>0.6177</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9353</v>
+        <v>-0.7195</v>
       </c>
       <c r="V19" t="n">
         <v>-0.113</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. DIAZ RODRIGUEZ</t>
+          <t>R. STUMBRIS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.8305</v>
+        <v>-5.5778</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0881</v>
+        <v>-3.0983</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.7424</v>
+        <v>-2.4795</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.2582</v>
+        <v>-5.485</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.612</v>
+        <v>-3.814</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6463</v>
+        <v>-1.671</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8234</v>
+        <v>-2.4319</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2492</v>
+        <v>-2.7977</v>
       </c>
       <c r="L20" t="n">
-        <v>1.0726</v>
+        <v>0.3658</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.0817</v>
+        <v>-3.053</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3628</v>
+        <v>-1.0162</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7188</v>
+        <v>-2.0368</v>
       </c>
       <c r="P20" t="n">
+        <v>0.6525</v>
+      </c>
+      <c r="Q20" t="n">
         <v>-1.0875</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-3.2626</v>
-      </c>
       <c r="R20" t="n">
-        <v>2.1751</v>
+        <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4163</v>
+        <v>-0.9406</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6489</v>
+        <v>0.2259</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7674</v>
+        <v>-1.1666</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0684</v>
+        <v>0.1952</v>
       </c>
       <c r="W20" t="n">
+        <v>0.1952</v>
+      </c>
+      <c r="X20" t="n">
         <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-1.0684</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.7603</v>
+        <v>-6.0666</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.634</v>
+        <v>-3.187</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1263</v>
+        <v>-2.8797</v>
       </c>
       <c r="G21" t="n">
         <v>-3.3816</v>
@@ -2092,13 +2092,13 @@
         <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0481</v>
+        <v>-0.3545</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1646</v>
+        <v>0.6117</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.2128</v>
+        <v>-0.9661999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-1.243</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.7392</v>
+        <v>-7.7219</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.7735</v>
+        <v>-4.8794</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.9657</v>
+        <v>-2.8424</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8875</v>
@@ -2170,13 +2170,13 @@
         <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.004</v>
+        <v>-0.9866</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.1406</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.2505</v>
+        <v>-1.1272</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4552</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-23.72340000000001</v>
+        <v>-23.7232</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.501599999999998</v>
+        <v>-9.501399999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-14.2219</v>
+        <v>-14.2217</v>
       </c>
       <c r="G23" t="n">
         <v>-13.6148</v>
@@ -2242,16 +2242,16 @@
         <v>-8.700299999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>-21.75069999999999</v>
+        <v>-21.7507</v>
       </c>
       <c r="R23" t="n">
         <v>13.0504</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.5175</v>
+        <v>-2.5174</v>
       </c>
       <c r="T23" t="n">
-        <v>4.103800000000001</v>
+        <v>4.103899999999999</v>
       </c>
       <c r="U23" t="n">
         <v>-6.6215</v>
